--- a/static/excel/F_model.xlsx
+++ b/static/excel/F_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -389,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -633,9 +633,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="22" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7375,11 +7372,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>56633.272816</v>
+        <v>58433.639471</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $14.47</t>
+          <t>FMP marketCap  |  price $14.93</t>
         </is>
       </c>
     </row>
@@ -7461,11 +7458,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7473,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7544,11 +7541,11 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Damodaran re-levered  (D/E = 2.91x,  t = 31.0%)</t>
+          <t>Damodaran re-levered  (D/E = 2.82x,  t = 31.0%)</t>
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>3.008</v>
+        <v>2.946</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7562,7 +7559,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>2.039</v>
+        <v>2.018</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7736,11 +7733,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0806</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 3.60%</t>
+          <t>Rf 4.57% + spread 3.60%</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7776,7 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0442</v>
+        <v>0.0447</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
@@ -7844,16 +7841,16 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B45" s="55">
-        <f>B8*B28+B9*B38*(1-B42)</f>
+        <f>MAX(0.085, B8*B28+B9*B38*(1-B42))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8216,13 +8213,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.0336</v>
+        <v>0.0351</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>-0.0081</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.0425</v>
+        <v>0.0431</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8566,13 +8563,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>193550.9</v>
+        <v>193842.3</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>191992.8</v>
+        <v>192137.1</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>200158.3</v>
+        <v>200424.3</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8600,27 +8597,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>184,827 — 202,761</t>
+          <t>185,105 — 203,066</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>177,540 — 204,969</t>
+          <t>177,674 — 205,123</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>193,245 — 207,072</t>
+          <t>193,378 — 207,471</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>186,336 — 211,017</t>
+          <t>186,111 — 210,762</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>195,987 — 221,946</t>
+          <t>195,751 — 221,679</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8641,10 +8638,10 @@
         </is>
       </c>
       <c r="G17" s="84" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="84" t="n">
         <v>9</v>
-      </c>
-      <c r="H17" s="85" t="n">
-        <v>10</v>
       </c>
       <c r="I17" s="84" t="n">
         <v>6</v>
@@ -8652,7 +8649,7 @@
       <c r="J17" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="86" t="n">
+      <c r="K17" s="85" t="n">
         <v>3</v>
       </c>
       <c r="L17" s="83" t="inlineStr">
@@ -8672,48 +8669,48 @@
           <t xml:space="preserve">  YoY Revenue Growth %</t>
         </is>
       </c>
-      <c r="B18" s="87" t="inlineStr">
+      <c r="B18" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C18" s="88">
+      <c r="C18" s="87">
         <f>IFERROR(C15/B15-1,"")</f>
         <v/>
       </c>
-      <c r="D18" s="88">
+      <c r="D18" s="87">
         <f>IFERROR(D15/C15-1,"")</f>
         <v/>
       </c>
-      <c r="E18" s="88">
+      <c r="E18" s="87">
         <f>IFERROR(E15/D15-1,"")</f>
         <v/>
       </c>
-      <c r="F18" s="88">
+      <c r="F18" s="87">
         <f>IFERROR(F15/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="89">
+      <c r="G18" s="88">
         <f>IFERROR(G15/F15-1,"")</f>
         <v/>
       </c>
-      <c r="H18" s="89">
+      <c r="H18" s="88">
         <f>IFERROR(H15/G15-1,"")</f>
         <v/>
       </c>
-      <c r="I18" s="89">
+      <c r="I18" s="88">
         <f>IFERROR(I15/H15-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="89">
+      <c r="J18" s="88">
         <f>IFERROR(J15/I15-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="89">
+      <c r="K18" s="88">
         <f>IFERROR(K15/J15-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="90">
+      <c r="L18" s="89">
         <f>L7</f>
         <v/>
       </c>
@@ -8764,13 +8761,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>12952.2</v>
+        <v>12971.7</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>12847.9</v>
+        <v>12857.6</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>13394.4</v>
+        <v>13412.2</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8798,27 +8795,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>12,368 — 13,569</t>
+          <t>12,387 — 13,589</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>11,881 — 13,716</t>
+          <t>11,890 — 13,727</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>12,932 — 13,857</t>
+          <t>12,941 — 13,884</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>12,469 — 14,121</t>
+          <t>12,454 — 14,104</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>13,115 — 14,852</t>
+          <t>13,099 — 14,834</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -8838,47 +8835,47 @@
           <t xml:space="preserve">  EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B22" s="88">
+      <c r="B22" s="87">
         <f>IFERROR(B20/B15,"")</f>
         <v/>
       </c>
-      <c r="C22" s="88">
+      <c r="C22" s="87">
         <f>IFERROR(C20/C15,"")</f>
         <v/>
       </c>
-      <c r="D22" s="88">
+      <c r="D22" s="87">
         <f>IFERROR(D20/D15,"")</f>
         <v/>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="87">
         <f>IFERROR(E20/E15,"")</f>
         <v/>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="87">
         <f>IFERROR(F20/F15,"")</f>
         <v/>
       </c>
-      <c r="G22" s="89">
+      <c r="G22" s="88">
         <f>IFERROR(G20/G15,"")</f>
         <v/>
       </c>
-      <c r="H22" s="89">
+      <c r="H22" s="88">
         <f>IFERROR(H20/H15,"")</f>
         <v/>
       </c>
-      <c r="I22" s="89">
+      <c r="I22" s="88">
         <f>IFERROR(I20/I15,"")</f>
         <v/>
       </c>
-      <c r="J22" s="89">
+      <c r="J22" s="88">
         <f>IFERROR(J20/J15,"")</f>
         <v/>
       </c>
-      <c r="K22" s="89">
+      <c r="K22" s="88">
         <f>IFERROR(K20/K15,"")</f>
         <v/>
       </c>
-      <c r="L22" s="90">
+      <c r="L22" s="89">
         <f>IFERROR(L20/L15,"")</f>
         <v/>
       </c>
@@ -8910,7 +8907,7 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="91" t="inlineStr">
+      <c r="A25" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  Less: D&amp;A</t>
         </is>
@@ -8935,23 +8932,23 @@
         <f>-'P&amp;L'!F14</f>
         <v/>
       </c>
-      <c r="G25" s="92">
+      <c r="G25" s="91">
         <f>-G15*G9</f>
         <v/>
       </c>
-      <c r="H25" s="92">
+      <c r="H25" s="91">
         <f>-H15*H9</f>
         <v/>
       </c>
-      <c r="I25" s="92">
+      <c r="I25" s="91">
         <f>-I15*I9</f>
         <v/>
       </c>
-      <c r="J25" s="92">
+      <c r="J25" s="91">
         <f>-J15*J9</f>
         <v/>
       </c>
-      <c r="K25" s="92">
+      <c r="K25" s="91">
         <f>-K15*K9</f>
         <v/>
       </c>
@@ -8970,47 +8967,47 @@
           <t>EBIT  (Operating Profit)</t>
         </is>
       </c>
-      <c r="B26" s="93">
+      <c r="B26" s="92">
         <f>B20+B25</f>
         <v/>
       </c>
-      <c r="C26" s="93">
+      <c r="C26" s="92">
         <f>C20+C25</f>
         <v/>
       </c>
-      <c r="D26" s="93">
+      <c r="D26" s="92">
         <f>D20+D25</f>
         <v/>
       </c>
-      <c r="E26" s="93">
+      <c r="E26" s="92">
         <f>E20+E25</f>
         <v/>
       </c>
-      <c r="F26" s="93">
+      <c r="F26" s="92">
         <f>F20+F25</f>
         <v/>
       </c>
-      <c r="G26" s="94">
+      <c r="G26" s="93">
         <f>G20+G25</f>
         <v/>
       </c>
-      <c r="H26" s="94">
+      <c r="H26" s="93">
         <f>H20+H25</f>
         <v/>
       </c>
-      <c r="I26" s="94">
+      <c r="I26" s="93">
         <f>I20+I25</f>
         <v/>
       </c>
-      <c r="J26" s="94">
+      <c r="J26" s="93">
         <f>J20+J25</f>
         <v/>
       </c>
-      <c r="K26" s="94">
+      <c r="K26" s="93">
         <f>K20+K25</f>
         <v/>
       </c>
-      <c r="L26" s="94">
+      <c r="L26" s="93">
         <f>L20+L25</f>
         <v/>
       </c>
@@ -9020,52 +9017,52 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="91" t="inlineStr">
+      <c r="A27" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  Less: Tax on EBIT  (unlevered)</t>
         </is>
       </c>
-      <c r="B27" s="95">
+      <c r="B27" s="94">
         <f>-B26*B12</f>
         <v/>
       </c>
-      <c r="C27" s="95">
+      <c r="C27" s="94">
         <f>-C26*C12</f>
         <v/>
       </c>
-      <c r="D27" s="95">
+      <c r="D27" s="94">
         <f>-D26*D12</f>
         <v/>
       </c>
-      <c r="E27" s="95">
+      <c r="E27" s="94">
         <f>-E26*E12</f>
         <v/>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="94">
         <f>-F26*F12</f>
         <v/>
       </c>
-      <c r="G27" s="96">
+      <c r="G27" s="95">
         <f>-G26*G12</f>
         <v/>
       </c>
-      <c r="H27" s="96">
+      <c r="H27" s="95">
         <f>-H26*H12</f>
         <v/>
       </c>
-      <c r="I27" s="96">
+      <c r="I27" s="95">
         <f>-I26*I12</f>
         <v/>
       </c>
-      <c r="J27" s="96">
+      <c r="J27" s="95">
         <f>-J26*J12</f>
         <v/>
       </c>
-      <c r="K27" s="96">
+      <c r="K27" s="95">
         <f>-K26*K12</f>
         <v/>
       </c>
-      <c r="L27" s="96">
+      <c r="L27" s="95">
         <f>-L26*L12</f>
         <v/>
       </c>
@@ -9080,47 +9077,47 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B28" s="93">
+      <c r="B28" s="92">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="93">
+      <c r="C28" s="92">
         <f>C26+C27</f>
         <v/>
       </c>
-      <c r="D28" s="93">
+      <c r="D28" s="92">
         <f>D26+D27</f>
         <v/>
       </c>
-      <c r="E28" s="93">
+      <c r="E28" s="92">
         <f>E26+E27</f>
         <v/>
       </c>
-      <c r="F28" s="93">
+      <c r="F28" s="92">
         <f>F26+F27</f>
         <v/>
       </c>
-      <c r="G28" s="97">
+      <c r="G28" s="96">
         <f>G26+G27</f>
         <v/>
       </c>
-      <c r="H28" s="97">
+      <c r="H28" s="96">
         <f>H26+H27</f>
         <v/>
       </c>
-      <c r="I28" s="97">
+      <c r="I28" s="96">
         <f>I26+I27</f>
         <v/>
       </c>
-      <c r="J28" s="97">
+      <c r="J28" s="96">
         <f>J26+J27</f>
         <v/>
       </c>
-      <c r="K28" s="97">
+      <c r="K28" s="96">
         <f>K26+K27</f>
         <v/>
       </c>
-      <c r="L28" s="97">
+      <c r="L28" s="96">
         <f>L26+L27</f>
         <v/>
       </c>
@@ -9130,52 +9127,52 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="91" t="inlineStr">
+      <c r="A29" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  (+) D&amp;A add-back  (non-cash)</t>
         </is>
       </c>
-      <c r="B29" s="95">
+      <c r="B29" s="94">
         <f>-B25</f>
         <v/>
       </c>
-      <c r="C29" s="95">
+      <c r="C29" s="94">
         <f>-C25</f>
         <v/>
       </c>
-      <c r="D29" s="95">
+      <c r="D29" s="94">
         <f>-D25</f>
         <v/>
       </c>
-      <c r="E29" s="95">
+      <c r="E29" s="94">
         <f>-E25</f>
         <v/>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="94">
         <f>-F25</f>
         <v/>
       </c>
-      <c r="G29" s="96">
+      <c r="G29" s="95">
         <f>-G25</f>
         <v/>
       </c>
-      <c r="H29" s="96">
+      <c r="H29" s="95">
         <f>-H25</f>
         <v/>
       </c>
-      <c r="I29" s="96">
+      <c r="I29" s="95">
         <f>-I25</f>
         <v/>
       </c>
-      <c r="J29" s="96">
+      <c r="J29" s="95">
         <f>-J25</f>
         <v/>
       </c>
-      <c r="K29" s="96">
+      <c r="K29" s="95">
         <f>-K25</f>
         <v/>
       </c>
-      <c r="L29" s="96">
+      <c r="L29" s="95">
         <f>-L25</f>
         <v/>
       </c>
@@ -9185,7 +9182,7 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="91" t="inlineStr">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  (−) Capital Expenditures</t>
         </is>
@@ -9210,27 +9207,27 @@
         <f>'Cash Flow'!F6</f>
         <v/>
       </c>
-      <c r="G30" s="96">
+      <c r="G30" s="95">
         <f>-G15*G10</f>
         <v/>
       </c>
-      <c r="H30" s="96">
+      <c r="H30" s="95">
         <f>-H15*H10</f>
         <v/>
       </c>
-      <c r="I30" s="96">
+      <c r="I30" s="95">
         <f>-I15*I10</f>
         <v/>
       </c>
-      <c r="J30" s="96">
+      <c r="J30" s="95">
         <f>-J15*J10</f>
         <v/>
       </c>
-      <c r="K30" s="96">
+      <c r="K30" s="95">
         <f>-K15*K10</f>
         <v/>
       </c>
-      <c r="L30" s="96">
+      <c r="L30" s="95">
         <f>-L15*L10</f>
         <v/>
       </c>
@@ -9240,49 +9237,49 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="91" t="inlineStr">
+      <c r="A31" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  (−) Increase in Net Working Capital</t>
         </is>
       </c>
-      <c r="B31" s="95" t="n"/>
-      <c r="C31" s="95">
+      <c r="B31" s="94" t="n"/>
+      <c r="C31" s="94">
         <f>-(('Balance Sheet'!C9-'Balance Sheet'!C21)-('Balance Sheet'!B9-'Balance Sheet'!B21))</f>
         <v/>
       </c>
-      <c r="D31" s="95">
+      <c r="D31" s="94">
         <f>-(('Balance Sheet'!D9-'Balance Sheet'!D21)-('Balance Sheet'!C9-'Balance Sheet'!C21))</f>
         <v/>
       </c>
-      <c r="E31" s="95">
+      <c r="E31" s="94">
         <f>-(('Balance Sheet'!E9-'Balance Sheet'!E21)-('Balance Sheet'!D9-'Balance Sheet'!D21))</f>
         <v/>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="94">
         <f>-(('Balance Sheet'!F9-'Balance Sheet'!F21)-('Balance Sheet'!E9-'Balance Sheet'!E21))</f>
         <v/>
       </c>
-      <c r="G31" s="96">
+      <c r="G31" s="95">
         <f>-G15*G11</f>
         <v/>
       </c>
-      <c r="H31" s="96">
+      <c r="H31" s="95">
         <f>-H15*H11</f>
         <v/>
       </c>
-      <c r="I31" s="96">
+      <c r="I31" s="95">
         <f>-I15*I11</f>
         <v/>
       </c>
-      <c r="J31" s="96">
+      <c r="J31" s="95">
         <f>-J15*J11</f>
         <v/>
       </c>
-      <c r="K31" s="96">
+      <c r="K31" s="95">
         <f>-K15*K11</f>
         <v/>
       </c>
-      <c r="L31" s="96">
+      <c r="L31" s="95">
         <f>-L15*L11</f>
         <v/>
       </c>
@@ -9297,47 +9294,47 @@
           <t>UNLEVERED FREE CASH FLOW  (UFCF)</t>
         </is>
       </c>
-      <c r="B32" s="93">
+      <c r="B32" s="92">
         <f>B28+B29+B30+B31</f>
         <v/>
       </c>
-      <c r="C32" s="93">
+      <c r="C32" s="92">
         <f>C28+C29+C30+C31</f>
         <v/>
       </c>
-      <c r="D32" s="93">
+      <c r="D32" s="92">
         <f>D28+D29+D30+D31</f>
         <v/>
       </c>
-      <c r="E32" s="93">
+      <c r="E32" s="92">
         <f>E28+E29+E30+E31</f>
         <v/>
       </c>
-      <c r="F32" s="93">
+      <c r="F32" s="92">
         <f>F28+F29+F30+F31</f>
         <v/>
       </c>
-      <c r="G32" s="97">
+      <c r="G32" s="96">
         <f>G28+G29+G30+G31</f>
         <v/>
       </c>
-      <c r="H32" s="97">
+      <c r="H32" s="96">
         <f>H28+H29+H30+H31</f>
         <v/>
       </c>
-      <c r="I32" s="97">
+      <c r="I32" s="96">
         <f>I28+I29+I30+I31</f>
         <v/>
       </c>
-      <c r="J32" s="97">
+      <c r="J32" s="96">
         <f>J28+J29+J30+J31</f>
         <v/>
       </c>
-      <c r="K32" s="97">
+      <c r="K32" s="96">
         <f>K28+K29+K30+K31</f>
         <v/>
       </c>
-      <c r="L32" s="97">
+      <c r="L32" s="96">
         <f>L28+L29+L30+L31</f>
         <v/>
       </c>
@@ -9352,47 +9349,47 @@
           <t xml:space="preserve">  UFCF Margin %</t>
         </is>
       </c>
-      <c r="B33" s="88">
+      <c r="B33" s="87">
         <f>B32/B15</f>
         <v/>
       </c>
-      <c r="C33" s="88">
+      <c r="C33" s="87">
         <f>C32/C15</f>
         <v/>
       </c>
-      <c r="D33" s="88">
+      <c r="D33" s="87">
         <f>D32/D15</f>
         <v/>
       </c>
-      <c r="E33" s="88">
+      <c r="E33" s="87">
         <f>E32/E15</f>
         <v/>
       </c>
-      <c r="F33" s="88">
+      <c r="F33" s="87">
         <f>F32/F15</f>
         <v/>
       </c>
-      <c r="G33" s="98">
+      <c r="G33" s="97">
         <f>IFERROR(G32/G15,"")</f>
         <v/>
       </c>
-      <c r="H33" s="98">
+      <c r="H33" s="97">
         <f>IFERROR(H32/H15,"")</f>
         <v/>
       </c>
-      <c r="I33" s="98">
+      <c r="I33" s="97">
         <f>IFERROR(I32/I15,"")</f>
         <v/>
       </c>
-      <c r="J33" s="98">
+      <c r="J33" s="97">
         <f>IFERROR(J32/J15,"")</f>
         <v/>
       </c>
-      <c r="K33" s="98">
+      <c r="K33" s="97">
         <f>IFERROR(K32/K15,"")</f>
         <v/>
       </c>
-      <c r="L33" s="98">
+      <c r="L33" s="97">
         <f>IFERROR(L32/L15,"")</f>
         <v/>
       </c>
@@ -9430,20 +9427,20 @@
           <t>WACC  (from WACC tab)</t>
         </is>
       </c>
-      <c r="B36" s="99">
+      <c r="B36" s="98">
         <f>WACC!B45</f>
         <v/>
       </c>
-      <c r="C36" s="100" t="n"/>
-      <c r="D36" s="100" t="n"/>
-      <c r="E36" s="100" t="n"/>
-      <c r="F36" s="100" t="n"/>
-      <c r="G36" s="100" t="n"/>
-      <c r="H36" s="100" t="n"/>
-      <c r="I36" s="100" t="n"/>
-      <c r="J36" s="100" t="n"/>
-      <c r="K36" s="100" t="n"/>
-      <c r="L36" s="100" t="n"/>
+      <c r="C36" s="99" t="n"/>
+      <c r="D36" s="99" t="n"/>
+      <c r="E36" s="99" t="n"/>
+      <c r="F36" s="99" t="n"/>
+      <c r="G36" s="99" t="n"/>
+      <c r="H36" s="99" t="n"/>
+      <c r="I36" s="99" t="n"/>
+      <c r="J36" s="99" t="n"/>
+      <c r="K36" s="99" t="n"/>
+      <c r="L36" s="99" t="n"/>
       <c r="M36" s="74" t="inlineStr">
         <is>
           <t>Auto-linked from WACC tab selected output.  Override manually if needed.</t>
@@ -9456,22 +9453,22 @@
           <t>Terminal Growth Rate  (g)</t>
         </is>
       </c>
-      <c r="B37" s="101" t="n">
+      <c r="B37" s="100" t="n">
         <v>0.03</v>
       </c>
-      <c r="C37" s="100" t="n"/>
-      <c r="D37" s="100" t="n"/>
-      <c r="E37" s="100" t="n"/>
-      <c r="F37" s="100" t="n"/>
-      <c r="G37" s="100" t="n"/>
-      <c r="H37" s="100" t="n"/>
-      <c r="I37" s="100" t="n"/>
-      <c r="J37" s="100" t="n"/>
-      <c r="K37" s="100" t="n"/>
-      <c r="L37" s="100" t="n"/>
+      <c r="C37" s="99" t="n"/>
+      <c r="D37" s="99" t="n"/>
+      <c r="E37" s="99" t="n"/>
+      <c r="F37" s="99" t="n"/>
+      <c r="G37" s="99" t="n"/>
+      <c r="H37" s="99" t="n"/>
+      <c r="I37" s="99" t="n"/>
+      <c r="J37" s="99" t="n"/>
+      <c r="K37" s="99" t="n"/>
+      <c r="L37" s="99" t="n"/>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: MEDIUM (5.9% 3yr avg rev growth).  Bear 2.25% / Base 3.0% / Bull 3.75%.  Keep below WACC.</t>
+          <t>Growth tier: MEDIUM (8.2% 3yr avg rev growth).  Bear 2.25% / Base 3.0% / Bull 3.75%.  Keep below WACC.</t>
         </is>
       </c>
     </row>
@@ -9481,22 +9478,22 @@
           <t>Terminal EV/EBITDA Multiple  (exit multiple method)</t>
         </is>
       </c>
-      <c r="B38" s="102" t="n">
+      <c r="B38" s="101" t="n">
         <v>15</v>
       </c>
-      <c r="C38" s="100" t="n"/>
-      <c r="D38" s="100" t="n"/>
-      <c r="E38" s="100" t="n"/>
-      <c r="F38" s="100" t="n"/>
-      <c r="G38" s="100" t="n"/>
-      <c r="H38" s="100" t="n"/>
-      <c r="I38" s="100" t="n"/>
-      <c r="J38" s="100" t="n"/>
-      <c r="K38" s="100" t="n"/>
-      <c r="L38" s="100" t="n"/>
+      <c r="C38" s="99" t="n"/>
+      <c r="D38" s="99" t="n"/>
+      <c r="E38" s="99" t="n"/>
+      <c r="F38" s="99" t="n"/>
+      <c r="G38" s="99" t="n"/>
+      <c r="H38" s="99" t="n"/>
+      <c r="I38" s="99" t="n"/>
+      <c r="J38" s="99" t="n"/>
+      <c r="K38" s="99" t="n"/>
+      <c r="L38" s="99" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: MEDIUM (5.9% 3yr avg rev growth).  Bear 11x / Base 15x / Bull 19x.  Override manually if needed.</t>
+          <t>Growth tier: MEDIUM (8.2% 3yr avg rev growth).  Bear 11x / Base 15x / Bull 19x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9516,25 +9513,25 @@
       <c r="M39" s="42" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="103" t="inlineStr">
+      <c r="A40" s="102" t="inlineStr">
         <is>
           <t>Terminal Year UFCF  (grown by g)</t>
         </is>
       </c>
-      <c r="B40" s="104">
+      <c r="B40" s="103">
         <f>L32</f>
         <v/>
       </c>
-      <c r="C40" s="105" t="n"/>
-      <c r="D40" s="105" t="n"/>
-      <c r="E40" s="105" t="n"/>
-      <c r="F40" s="105" t="n"/>
-      <c r="G40" s="105" t="n"/>
-      <c r="H40" s="105" t="n"/>
-      <c r="I40" s="105" t="n"/>
-      <c r="J40" s="105" t="n"/>
-      <c r="K40" s="105" t="n"/>
-      <c r="L40" s="105" t="n"/>
+      <c r="C40" s="104" t="n"/>
+      <c r="D40" s="104" t="n"/>
+      <c r="E40" s="104" t="n"/>
+      <c r="F40" s="104" t="n"/>
+      <c r="G40" s="104" t="n"/>
+      <c r="H40" s="104" t="n"/>
+      <c r="I40" s="104" t="n"/>
+      <c r="J40" s="104" t="n"/>
+      <c r="K40" s="104" t="n"/>
+      <c r="L40" s="104" t="n"/>
       <c r="M40" s="80" t="inlineStr">
         <is>
           <t>Cross-ref from Section 3 — terminal year UFCF (already grown by g in assumptions)</t>
@@ -9547,20 +9544,20 @@
           <t>Terminal Value  [Gordon Growth:  UFCF / (WACC − g)]</t>
         </is>
       </c>
-      <c r="B41" s="97">
+      <c r="B41" s="96">
         <f>B40/(B36-B37)</f>
         <v/>
       </c>
-      <c r="C41" s="106" t="n"/>
-      <c r="D41" s="106" t="n"/>
-      <c r="E41" s="106" t="n"/>
-      <c r="F41" s="106" t="n"/>
-      <c r="G41" s="106" t="n"/>
-      <c r="H41" s="106" t="n"/>
-      <c r="I41" s="106" t="n"/>
-      <c r="J41" s="106" t="n"/>
-      <c r="K41" s="106" t="n"/>
-      <c r="L41" s="106" t="n"/>
+      <c r="C41" s="105" t="n"/>
+      <c r="D41" s="105" t="n"/>
+      <c r="E41" s="105" t="n"/>
+      <c r="F41" s="105" t="n"/>
+      <c r="G41" s="105" t="n"/>
+      <c r="H41" s="105" t="n"/>
+      <c r="I41" s="105" t="n"/>
+      <c r="J41" s="105" t="n"/>
+      <c r="K41" s="105" t="n"/>
+      <c r="L41" s="105" t="n"/>
       <c r="M41" s="80" t="inlineStr">
         <is>
           <t>Sensitive to g — always cross-check vs Exit Multiple below</t>
@@ -9573,20 +9570,20 @@
           <t>Terminal Value  [Exit Multiple:  Terminal EBITDA × Multiple]</t>
         </is>
       </c>
-      <c r="B42" s="97">
+      <c r="B42" s="96">
         <f>L20*B38</f>
         <v/>
       </c>
-      <c r="C42" s="106" t="n"/>
-      <c r="D42" s="106" t="n"/>
-      <c r="E42" s="106" t="n"/>
-      <c r="F42" s="106" t="n"/>
-      <c r="G42" s="106" t="n"/>
-      <c r="H42" s="106" t="n"/>
-      <c r="I42" s="106" t="n"/>
-      <c r="J42" s="106" t="n"/>
-      <c r="K42" s="106" t="n"/>
-      <c r="L42" s="106" t="n"/>
+      <c r="C42" s="105" t="n"/>
+      <c r="D42" s="105" t="n"/>
+      <c r="E42" s="105" t="n"/>
+      <c r="F42" s="105" t="n"/>
+      <c r="G42" s="105" t="n"/>
+      <c r="H42" s="105" t="n"/>
+      <c r="I42" s="105" t="n"/>
+      <c r="J42" s="105" t="n"/>
+      <c r="K42" s="105" t="n"/>
+      <c r="L42" s="105" t="n"/>
       <c r="M42" s="80" t="inlineStr">
         <is>
           <t>Anchored to observable market multiples — less model-sensitive than Gordon Growth</t>
@@ -9616,27 +9613,27 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="103" t="inlineStr">
+      <c r="A45" s="102" t="inlineStr">
         <is>
           <t>Discount Period  (mid-year convention)</t>
         </is>
       </c>
-      <c r="G45" s="107" t="n">
+      <c r="G45" s="106" t="n">
         <v>0.5</v>
       </c>
-      <c r="H45" s="107" t="n">
+      <c r="H45" s="106" t="n">
         <v>1.5</v>
       </c>
-      <c r="I45" s="107" t="n">
+      <c r="I45" s="106" t="n">
         <v>2.5</v>
       </c>
-      <c r="J45" s="107" t="n">
+      <c r="J45" s="106" t="n">
         <v>3.5</v>
       </c>
-      <c r="K45" s="107" t="n">
+      <c r="K45" s="106" t="n">
         <v>4.5</v>
       </c>
-      <c r="L45" s="108" t="n">
+      <c r="L45" s="107" t="n">
         <v>5</v>
       </c>
       <c r="M45" s="80" t="inlineStr">
@@ -9646,32 +9643,32 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="103" t="inlineStr">
+      <c r="A46" s="102" t="inlineStr">
         <is>
           <t>Discount Factor  =  1 / (1 + WACC) ^ period</t>
         </is>
       </c>
-      <c r="G46" s="109">
+      <c r="G46" s="108">
         <f>1/(1+B36)^G45</f>
         <v/>
       </c>
-      <c r="H46" s="109">
+      <c r="H46" s="108">
         <f>1/(1+B36)^H45</f>
         <v/>
       </c>
-      <c r="I46" s="109">
+      <c r="I46" s="108">
         <f>1/(1+B36)^I45</f>
         <v/>
       </c>
-      <c r="J46" s="109">
+      <c r="J46" s="108">
         <f>1/(1+B36)^J45</f>
         <v/>
       </c>
-      <c r="K46" s="109">
+      <c r="K46" s="108">
         <f>1/(1+B36)^K45</f>
         <v/>
       </c>
-      <c r="L46" s="110">
+      <c r="L46" s="109">
         <f>1/(1+B36)^L45</f>
         <v/>
       </c>
@@ -9686,27 +9683,27 @@
           <t>PV of UFCF</t>
         </is>
       </c>
-      <c r="G47" s="97">
+      <c r="G47" s="96">
         <f>G32*G46</f>
         <v/>
       </c>
-      <c r="H47" s="97">
+      <c r="H47" s="96">
         <f>H32*H46</f>
         <v/>
       </c>
-      <c r="I47" s="97">
+      <c r="I47" s="96">
         <f>I32*I46</f>
         <v/>
       </c>
-      <c r="J47" s="97">
+      <c r="J47" s="96">
         <f>J32*J46</f>
         <v/>
       </c>
-      <c r="K47" s="97">
+      <c r="K47" s="96">
         <f>K32*K46</f>
         <v/>
       </c>
-      <c r="L47" s="106" t="n"/>
+      <c r="L47" s="105" t="n"/>
       <c r="M47" s="80">
         <f> UFCF × discount factor</f>
         <v/>
@@ -9718,20 +9715,20 @@
           <t>Sum of PV of FCFs  (explicit period)</t>
         </is>
       </c>
-      <c r="B48" s="94">
+      <c r="B48" s="93">
         <f>G47+H47+I47+J47+K47</f>
         <v/>
       </c>
-      <c r="C48" s="111" t="n"/>
-      <c r="D48" s="111" t="n"/>
-      <c r="E48" s="111" t="n"/>
-      <c r="F48" s="111" t="n"/>
-      <c r="G48" s="111" t="n"/>
-      <c r="H48" s="111" t="n"/>
-      <c r="I48" s="111" t="n"/>
-      <c r="J48" s="111" t="n"/>
-      <c r="K48" s="111" t="n"/>
-      <c r="L48" s="111" t="n"/>
+      <c r="C48" s="110" t="n"/>
+      <c r="D48" s="110" t="n"/>
+      <c r="E48" s="110" t="n"/>
+      <c r="F48" s="110" t="n"/>
+      <c r="G48" s="110" t="n"/>
+      <c r="H48" s="110" t="n"/>
+      <c r="I48" s="110" t="n"/>
+      <c r="J48" s="110" t="n"/>
+      <c r="K48" s="110" t="n"/>
+      <c r="L48" s="110" t="n"/>
       <c r="M48" s="80" t="inlineStr">
         <is>
           <t>Sum of 5 discounted annual FCFs</t>
@@ -9744,20 +9741,20 @@
           <t>PV of Terminal Value  [Gordon Growth]</t>
         </is>
       </c>
-      <c r="B49" s="94">
+      <c r="B49" s="93">
         <f>B41*L46</f>
         <v/>
       </c>
-      <c r="C49" s="111" t="n"/>
-      <c r="D49" s="111" t="n"/>
-      <c r="E49" s="111" t="n"/>
-      <c r="F49" s="111" t="n"/>
-      <c r="G49" s="111" t="n"/>
-      <c r="H49" s="111" t="n"/>
-      <c r="I49" s="111" t="n"/>
-      <c r="J49" s="111" t="n"/>
-      <c r="K49" s="111" t="n"/>
-      <c r="L49" s="111" t="n"/>
+      <c r="C49" s="110" t="n"/>
+      <c r="D49" s="110" t="n"/>
+      <c r="E49" s="110" t="n"/>
+      <c r="F49" s="110" t="n"/>
+      <c r="G49" s="110" t="n"/>
+      <c r="H49" s="110" t="n"/>
+      <c r="I49" s="110" t="n"/>
+      <c r="J49" s="110" t="n"/>
+      <c r="K49" s="110" t="n"/>
+      <c r="L49" s="110" t="n"/>
       <c r="M49" s="80" t="inlineStr">
         <is>
           <t>Terminal value × terminal-year discount factor</t>
@@ -9770,20 +9767,20 @@
           <t>PV of Terminal Value  [Exit Multiple]</t>
         </is>
       </c>
-      <c r="B50" s="94">
+      <c r="B50" s="93">
         <f>B42*L46</f>
         <v/>
       </c>
-      <c r="C50" s="111" t="n"/>
-      <c r="D50" s="111" t="n"/>
-      <c r="E50" s="111" t="n"/>
-      <c r="F50" s="111" t="n"/>
-      <c r="G50" s="111" t="n"/>
-      <c r="H50" s="111" t="n"/>
-      <c r="I50" s="111" t="n"/>
-      <c r="J50" s="111" t="n"/>
-      <c r="K50" s="111" t="n"/>
-      <c r="L50" s="111" t="n"/>
+      <c r="C50" s="110" t="n"/>
+      <c r="D50" s="110" t="n"/>
+      <c r="E50" s="110" t="n"/>
+      <c r="F50" s="110" t="n"/>
+      <c r="G50" s="110" t="n"/>
+      <c r="H50" s="110" t="n"/>
+      <c r="I50" s="110" t="n"/>
+      <c r="J50" s="110" t="n"/>
+      <c r="K50" s="110" t="n"/>
+      <c r="L50" s="110" t="n"/>
       <c r="M50" s="80" t="inlineStr">
         <is>
           <t>Terminal value × terminal-year discount factor</t>
@@ -9818,21 +9815,21 @@
           <t>Enterprise Value  [Gordon Growth]</t>
         </is>
       </c>
-      <c r="B53" s="97">
+      <c r="B53" s="96">
         <f>B48+B49</f>
         <v/>
       </c>
-      <c r="C53" s="106" t="n"/>
-      <c r="D53" s="106" t="n"/>
-      <c r="E53" s="106" t="n"/>
-      <c r="F53" s="106" t="n"/>
-      <c r="G53" s="106" t="n"/>
-      <c r="H53" s="106" t="n"/>
-      <c r="I53" s="106" t="n"/>
-      <c r="J53" s="106" t="n"/>
-      <c r="K53" s="106" t="n"/>
-      <c r="L53" s="106" t="n"/>
-      <c r="M53" s="106" t="n"/>
+      <c r="C53" s="105" t="n"/>
+      <c r="D53" s="105" t="n"/>
+      <c r="E53" s="105" t="n"/>
+      <c r="F53" s="105" t="n"/>
+      <c r="G53" s="105" t="n"/>
+      <c r="H53" s="105" t="n"/>
+      <c r="I53" s="105" t="n"/>
+      <c r="J53" s="105" t="n"/>
+      <c r="K53" s="105" t="n"/>
+      <c r="L53" s="105" t="n"/>
+      <c r="M53" s="105" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="75" t="inlineStr">
@@ -9840,42 +9837,42 @@
           <t>Enterprise Value  [Exit Multiple]</t>
         </is>
       </c>
-      <c r="B54" s="97">
+      <c r="B54" s="96">
         <f>B48+B50</f>
         <v/>
       </c>
-      <c r="C54" s="106" t="n"/>
-      <c r="D54" s="106" t="n"/>
-      <c r="E54" s="106" t="n"/>
-      <c r="F54" s="106" t="n"/>
-      <c r="G54" s="106" t="n"/>
-      <c r="H54" s="106" t="n"/>
-      <c r="I54" s="106" t="n"/>
-      <c r="J54" s="106" t="n"/>
-      <c r="K54" s="106" t="n"/>
-      <c r="L54" s="106" t="n"/>
-      <c r="M54" s="106" t="n"/>
+      <c r="C54" s="105" t="n"/>
+      <c r="D54" s="105" t="n"/>
+      <c r="E54" s="105" t="n"/>
+      <c r="F54" s="105" t="n"/>
+      <c r="G54" s="105" t="n"/>
+      <c r="H54" s="105" t="n"/>
+      <c r="I54" s="105" t="n"/>
+      <c r="J54" s="105" t="n"/>
+      <c r="K54" s="105" t="n"/>
+      <c r="L54" s="105" t="n"/>
+      <c r="M54" s="105" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="91" t="inlineStr">
+      <c r="A55" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  Less: Net Debt  (Debt − Cash)</t>
         </is>
       </c>
-      <c r="B55" s="104">
+      <c r="B55" s="103">
         <f>'Balance Sheet'!F81</f>
         <v/>
       </c>
-      <c r="C55" s="105" t="n"/>
-      <c r="D55" s="105" t="n"/>
-      <c r="E55" s="105" t="n"/>
-      <c r="F55" s="105" t="n"/>
-      <c r="G55" s="105" t="n"/>
-      <c r="H55" s="105" t="n"/>
-      <c r="I55" s="105" t="n"/>
-      <c r="J55" s="105" t="n"/>
-      <c r="K55" s="105" t="n"/>
-      <c r="L55" s="105" t="n"/>
+      <c r="C55" s="104" t="n"/>
+      <c r="D55" s="104" t="n"/>
+      <c r="E55" s="104" t="n"/>
+      <c r="F55" s="104" t="n"/>
+      <c r="G55" s="104" t="n"/>
+      <c r="H55" s="104" t="n"/>
+      <c r="I55" s="104" t="n"/>
+      <c r="J55" s="104" t="n"/>
+      <c r="K55" s="104" t="n"/>
+      <c r="L55" s="104" t="n"/>
       <c r="M55" s="80" t="inlineStr">
         <is>
           <t>Linked from Balance Sheet: Total Debt (ST+LT) − Cash &amp; Equivalents  (negative = net cash)</t>
@@ -9883,24 +9880,24 @@
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="91" t="inlineStr">
+      <c r="A56" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  Less: Minority Interest</t>
         </is>
       </c>
-      <c r="B56" s="104" t="n">
+      <c r="B56" s="103" t="n">
         <v>28</v>
       </c>
-      <c r="C56" s="105" t="n"/>
-      <c r="D56" s="105" t="n"/>
-      <c r="E56" s="105" t="n"/>
-      <c r="F56" s="105" t="n"/>
-      <c r="G56" s="105" t="n"/>
-      <c r="H56" s="105" t="n"/>
-      <c r="I56" s="105" t="n"/>
-      <c r="J56" s="105" t="n"/>
-      <c r="K56" s="105" t="n"/>
-      <c r="L56" s="105" t="n"/>
+      <c r="C56" s="104" t="n"/>
+      <c r="D56" s="104" t="n"/>
+      <c r="E56" s="104" t="n"/>
+      <c r="F56" s="104" t="n"/>
+      <c r="G56" s="104" t="n"/>
+      <c r="H56" s="104" t="n"/>
+      <c r="I56" s="104" t="n"/>
+      <c r="J56" s="104" t="n"/>
+      <c r="K56" s="104" t="n"/>
+      <c r="L56" s="104" t="n"/>
       <c r="M56" s="80" t="inlineStr">
         <is>
           <t>Auto-linked from Balance Sheet: minorityInterest</t>
@@ -9908,24 +9905,24 @@
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="91" t="inlineStr">
+      <c r="A57" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  Shares Outstanding — Diluted  (mm)</t>
         </is>
       </c>
-      <c r="B57" s="104" t="n">
+      <c r="B57" s="103" t="n">
         <v>3979</v>
       </c>
-      <c r="C57" s="105" t="n"/>
-      <c r="D57" s="105" t="n"/>
-      <c r="E57" s="105" t="n"/>
-      <c r="F57" s="105" t="n"/>
-      <c r="G57" s="105" t="n"/>
-      <c r="H57" s="105" t="n"/>
-      <c r="I57" s="105" t="n"/>
-      <c r="J57" s="105" t="n"/>
-      <c r="K57" s="105" t="n"/>
-      <c r="L57" s="105" t="n"/>
+      <c r="C57" s="104" t="n"/>
+      <c r="D57" s="104" t="n"/>
+      <c r="E57" s="104" t="n"/>
+      <c r="F57" s="104" t="n"/>
+      <c r="G57" s="104" t="n"/>
+      <c r="H57" s="104" t="n"/>
+      <c r="I57" s="104" t="n"/>
+      <c r="J57" s="104" t="n"/>
+      <c r="K57" s="104" t="n"/>
+      <c r="L57" s="104" t="n"/>
       <c r="M57" s="80" t="inlineStr">
         <is>
           <t>Auto-linked: weightedAverageShsOutDil from income statement (diluted)</t>
@@ -9953,21 +9950,21 @@
           <t>Implied Share Price  [Gordon Growth]  ($)</t>
         </is>
       </c>
-      <c r="B59" s="112">
+      <c r="B59" s="111">
         <f>IFERROR((B53-B55-B56)/B57,"")</f>
         <v/>
       </c>
-      <c r="C59" s="106" t="n"/>
-      <c r="D59" s="106" t="n"/>
-      <c r="E59" s="106" t="n"/>
-      <c r="F59" s="106" t="n"/>
-      <c r="G59" s="106" t="n"/>
-      <c r="H59" s="106" t="n"/>
-      <c r="I59" s="106" t="n"/>
-      <c r="J59" s="106" t="n"/>
-      <c r="K59" s="106" t="n"/>
-      <c r="L59" s="106" t="n"/>
-      <c r="M59" s="106" t="n"/>
+      <c r="C59" s="105" t="n"/>
+      <c r="D59" s="105" t="n"/>
+      <c r="E59" s="105" t="n"/>
+      <c r="F59" s="105" t="n"/>
+      <c r="G59" s="105" t="n"/>
+      <c r="H59" s="105" t="n"/>
+      <c r="I59" s="105" t="n"/>
+      <c r="J59" s="105" t="n"/>
+      <c r="K59" s="105" t="n"/>
+      <c r="L59" s="105" t="n"/>
+      <c r="M59" s="105" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="75" t="inlineStr">
@@ -9975,41 +9972,41 @@
           <t>Implied Share Price  [Exit Multiple]  ($)</t>
         </is>
       </c>
-      <c r="B60" s="112">
+      <c r="B60" s="111">
         <f>IFERROR((B54-B55-B56)/B57,"")</f>
         <v/>
       </c>
-      <c r="C60" s="106" t="n"/>
-      <c r="D60" s="106" t="n"/>
-      <c r="E60" s="106" t="n"/>
-      <c r="F60" s="106" t="n"/>
-      <c r="G60" s="106" t="n"/>
-      <c r="H60" s="106" t="n"/>
-      <c r="I60" s="106" t="n"/>
-      <c r="J60" s="106" t="n"/>
-      <c r="K60" s="106" t="n"/>
-      <c r="L60" s="106" t="n"/>
-      <c r="M60" s="106" t="n"/>
+      <c r="C60" s="105" t="n"/>
+      <c r="D60" s="105" t="n"/>
+      <c r="E60" s="105" t="n"/>
+      <c r="F60" s="105" t="n"/>
+      <c r="G60" s="105" t="n"/>
+      <c r="H60" s="105" t="n"/>
+      <c r="I60" s="105" t="n"/>
+      <c r="J60" s="105" t="n"/>
+      <c r="K60" s="105" t="n"/>
+      <c r="L60" s="105" t="n"/>
+      <c r="M60" s="105" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="103" t="inlineStr">
+      <c r="A61" s="102" t="inlineStr">
         <is>
           <t>Current Market Price  ($)</t>
         </is>
       </c>
-      <c r="B61" s="113" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="C61" s="105" t="n"/>
-      <c r="D61" s="105" t="n"/>
-      <c r="E61" s="105" t="n"/>
-      <c r="F61" s="105" t="n"/>
-      <c r="G61" s="105" t="n"/>
-      <c r="H61" s="105" t="n"/>
-      <c r="I61" s="105" t="n"/>
-      <c r="J61" s="105" t="n"/>
-      <c r="K61" s="105" t="n"/>
-      <c r="L61" s="105" t="n"/>
+      <c r="B61" s="112" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="C61" s="104" t="n"/>
+      <c r="D61" s="104" t="n"/>
+      <c r="E61" s="104" t="n"/>
+      <c r="F61" s="104" t="n"/>
+      <c r="G61" s="104" t="n"/>
+      <c r="H61" s="104" t="n"/>
+      <c r="I61" s="104" t="n"/>
+      <c r="J61" s="104" t="n"/>
+      <c r="K61" s="104" t="n"/>
+      <c r="L61" s="104" t="n"/>
       <c r="M61" s="80" t="inlineStr">
         <is>
           <t>Auto-linked from FMP company profile — price</t>
@@ -10022,21 +10019,21 @@
           <t>Upside / (Downside)  [Gordon Growth]</t>
         </is>
       </c>
-      <c r="B62" s="114">
+      <c r="B62" s="113">
         <f>IFERROR(B59/B61-1,"")</f>
         <v/>
       </c>
-      <c r="C62" s="111" t="n"/>
-      <c r="D62" s="111" t="n"/>
-      <c r="E62" s="111" t="n"/>
-      <c r="F62" s="111" t="n"/>
-      <c r="G62" s="111" t="n"/>
-      <c r="H62" s="111" t="n"/>
-      <c r="I62" s="111" t="n"/>
-      <c r="J62" s="111" t="n"/>
-      <c r="K62" s="111" t="n"/>
-      <c r="L62" s="111" t="n"/>
-      <c r="M62" s="111" t="n"/>
+      <c r="C62" s="110" t="n"/>
+      <c r="D62" s="110" t="n"/>
+      <c r="E62" s="110" t="n"/>
+      <c r="F62" s="110" t="n"/>
+      <c r="G62" s="110" t="n"/>
+      <c r="H62" s="110" t="n"/>
+      <c r="I62" s="110" t="n"/>
+      <c r="J62" s="110" t="n"/>
+      <c r="K62" s="110" t="n"/>
+      <c r="L62" s="110" t="n"/>
+      <c r="M62" s="110" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="63" t="inlineStr">
@@ -10044,21 +10041,21 @@
           <t>Upside / (Downside)  [Exit Multiple]</t>
         </is>
       </c>
-      <c r="B63" s="114">
+      <c r="B63" s="113">
         <f>IFERROR(B60/B61-1,"")</f>
         <v/>
       </c>
-      <c r="C63" s="111" t="n"/>
-      <c r="D63" s="111" t="n"/>
-      <c r="E63" s="111" t="n"/>
-      <c r="F63" s="111" t="n"/>
-      <c r="G63" s="111" t="n"/>
-      <c r="H63" s="111" t="n"/>
-      <c r="I63" s="111" t="n"/>
-      <c r="J63" s="111" t="n"/>
-      <c r="K63" s="111" t="n"/>
-      <c r="L63" s="111" t="n"/>
-      <c r="M63" s="111" t="n"/>
+      <c r="C63" s="110" t="n"/>
+      <c r="D63" s="110" t="n"/>
+      <c r="E63" s="110" t="n"/>
+      <c r="F63" s="110" t="n"/>
+      <c r="G63" s="110" t="n"/>
+      <c r="H63" s="110" t="n"/>
+      <c r="I63" s="110" t="n"/>
+      <c r="J63" s="110" t="n"/>
+      <c r="K63" s="110" t="n"/>
+      <c r="L63" s="110" t="n"/>
+      <c r="M63" s="110" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -10096,14 +10093,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
-        <is>
-          <t>JS SCORECARD — F  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Cyclical</t>
+      <c r="A1" s="114" t="inlineStr">
+        <is>
+          <t>JS SCORECARD — F  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Cyclical</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="116" t="inlineStr">
+      <c r="A2" s="115" t="inlineStr">
         <is>
           <t>Blue rows = auto-scored (FMP data + yfinance proxies).  Yellow rows = manual — select tier from dropdown in column E.  Only 2 criteria require manual input: Business Clarity + Long-Term Potential.  Score: HIGH=10 | MOD-HIGH=7 | MOD-LOW=3 | LOW=0</t>
         </is>
@@ -10120,7 +10117,7 @@
       <c r="H3" s="42" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="117" t="inlineStr">
+      <c r="A4" s="116" t="inlineStr">
         <is>
           <t>⚠  SOFT FLOOR CAP 40/100 applied — D/EBITDA 19.3x → −81.6 pts  |  EBIT/Interest 2.0x → −3.9 pts  (kicks in at D/EBITDA &gt; 3.0x or EBIT/Int &lt; 3.0x; smooth, no cliffs)</t>
         </is>
@@ -10137,42 +10134,42 @@
       <c r="H5" s="42" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="118" t="inlineStr">
+      <c r="A6" s="117" t="inlineStr">
         <is>
           <t>CRITERION</t>
         </is>
       </c>
-      <c r="B6" s="119" t="inlineStr">
+      <c r="B6" s="118" t="inlineStr">
         <is>
           <t>PART</t>
         </is>
       </c>
-      <c r="C6" s="119" t="inlineStr">
+      <c r="C6" s="118" t="inlineStr">
         <is>
           <t>WEIGHT %</t>
         </is>
       </c>
-      <c r="D6" s="119" t="inlineStr">
+      <c r="D6" s="118" t="inlineStr">
         <is>
           <t>CALCULATED VALUE</t>
         </is>
       </c>
-      <c r="E6" s="119" t="inlineStr">
+      <c r="E6" s="118" t="inlineStr">
         <is>
           <t>TIER  ▼</t>
         </is>
       </c>
-      <c r="F6" s="119" t="inlineStr">
+      <c r="F6" s="118" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
-      <c r="G6" s="119" t="inlineStr">
+      <c r="G6" s="118" t="inlineStr">
         <is>
           <t>WTD SCORE</t>
         </is>
       </c>
-      <c r="H6" s="118" t="inlineStr">
+      <c r="H6" s="117" t="inlineStr">
         <is>
           <t>NOTES / COMMENTARY (editable)</t>
         </is>
@@ -10186,136 +10183,136 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="120" t="inlineStr">
+      <c r="A8" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Business Clarity</t>
         </is>
       </c>
-      <c r="B8" s="121" t="inlineStr">
+      <c r="B8" s="120" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C8" s="122" t="n">
+      <c r="C8" s="121" t="n">
         <v>0.025</v>
       </c>
-      <c r="D8" s="123" t="inlineStr">
+      <c r="D8" s="122" t="inlineStr">
         <is>
           <t>— user input required</t>
         </is>
       </c>
-      <c r="E8" s="124" t="n"/>
-      <c r="F8" s="125">
+      <c r="E8" s="123" t="n"/>
+      <c r="F8" s="124">
         <f>IF(E8="HIGH",10,IF(E8="MOD-HIGH",7,IF(E8="MOD-LOW",3,IF(E8="LOW",0,""))))</f>
         <v/>
       </c>
-      <c r="G8" s="126">
+      <c r="G8" s="125">
         <f>IF(F8="",0,C8*F8*10)</f>
         <v/>
       </c>
-      <c r="H8" s="127" t="inlineStr"/>
+      <c r="H8" s="126" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Moat Profile</t>
         </is>
       </c>
-      <c r="B9" s="129" t="inlineStr">
+      <c r="B9" s="128" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C9" s="130" t="n">
+      <c r="C9" s="129" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="131" t="inlineStr">
-        <is>
-          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC +0.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
-        </is>
-      </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="D9" s="130" t="inlineStr">
+        <is>
+          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+        </is>
+      </c>
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F9" s="133" t="n">
+      <c r="F9" s="132" t="n">
         <v>2.5</v>
       </c>
-      <c r="G9" s="134">
+      <c r="G9" s="133">
         <f>IF(F9="",0,C9*F9*10)</f>
         <v/>
       </c>
-      <c r="H9" s="135" t="inlineStr">
-        <is>
-          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC +0.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+      <c r="H9" s="134" t="inlineStr">
+        <is>
+          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="120" t="inlineStr">
+      <c r="A10" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">  Long-Term Potential</t>
         </is>
       </c>
-      <c r="B10" s="121" t="inlineStr">
+      <c r="B10" s="120" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C10" s="122" t="n">
+      <c r="C10" s="121" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="123" t="inlineStr">
+      <c r="D10" s="122" t="inlineStr">
         <is>
           <t>— user input required</t>
         </is>
       </c>
-      <c r="E10" s="124" t="n"/>
-      <c r="F10" s="125">
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="124">
         <f>IF(E10="HIGH",10,IF(E10="MOD-HIGH",7,IF(E10="MOD-LOW",3,IF(E10="LOW",0,""))))</f>
         <v/>
       </c>
-      <c r="G10" s="126">
+      <c r="G10" s="125">
         <f>IF(F10="",0,C10*F10*10)</f>
         <v/>
       </c>
-      <c r="H10" s="127" t="inlineStr"/>
+      <c r="H10" s="126" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Management</t>
         </is>
       </c>
-      <c r="B11" s="129" t="inlineStr">
+      <c r="B11" s="128" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="130" t="n">
+      <c r="C11" s="129" t="n">
         <v>0.075</v>
       </c>
-      <c r="D11" s="131" t="inlineStr">
-        <is>
-          <t>ROIC trend -1.9% ✓ (≥-2pp)  |  GM maintained -3.7% ✗  |  Op margin -2.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 1% ✓ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
-        </is>
-      </c>
-      <c r="E11" s="136" t="inlineStr">
+      <c r="D11" s="130" t="inlineStr">
+        <is>
+          <t>ROIC trend -1.9% ✓ (&gt;=-2pp)  |  GM maintained -3.7% ✗  |  Op margin -2.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 1% ✓ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
+        </is>
+      </c>
+      <c r="E11" s="135" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F11" s="133" t="n">
+      <c r="F11" s="132" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="134">
+      <c r="G11" s="133">
         <f>IF(F11="",0,C11*F11*10)</f>
         <v/>
       </c>
-      <c r="H11" s="135" t="inlineStr">
-        <is>
-          <t>ROIC trend -1.9% ✓ (≥-2pp)  |  GM maintained -3.7% ✗  |  Op margin -2.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 1% ✓ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
+      <c r="H11" s="134" t="inlineStr">
+        <is>
+          <t>ROIC trend -1.9% ✓ (&gt;=-2pp)  |  GM maintained -3.7% ✗  |  Op margin -2.7% ✗ (≥-2pp)  |  Capital returns LOW ✗  |  Share count -0.1%/yr ✓ (net buyback)  |  Goodwill/Equity 1% ✓ (&lt;40%)  [3/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10327,148 +10324,148 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue 3yr CAGR</t>
         </is>
       </c>
-      <c r="B13" s="129" t="inlineStr">
+      <c r="B13" s="128" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C13" s="130" t="n">
+      <c r="C13" s="129" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="131" t="inlineStr">
+      <c r="D13" s="130" t="inlineStr">
         <is>
           <t>5.8%</t>
         </is>
       </c>
-      <c r="E13" s="137" t="inlineStr">
+      <c r="E13" s="136" t="inlineStr">
         <is>
           <t>MOD-HIGH</t>
         </is>
       </c>
-      <c r="F13" s="133" t="n">
+      <c r="F13" s="132" t="n">
         <v>7.49</v>
       </c>
-      <c r="G13" s="134">
+      <c r="G13" s="133">
         <f>IF(F13="",0,C13*F13*10)</f>
         <v/>
       </c>
-      <c r="H13" s="135" t="inlineStr">
+      <c r="H13" s="134" t="inlineStr">
         <is>
           <t>5.8%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cash Quality  (FCF / Net Income)</t>
         </is>
       </c>
-      <c r="B14" s="129" t="inlineStr">
+      <c r="B14" s="128" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="130" t="n">
+      <c r="C14" s="129" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="131" t="inlineStr">
+      <c r="D14" s="130" t="inlineStr">
         <is>
           <t>53%  [trend penalty: declined &gt;15pp vs 3yr ago]  [through-cycle: 5yr median, latest -152.4% → smoothed 53.3%]</t>
         </is>
       </c>
-      <c r="E14" s="136" t="inlineStr">
+      <c r="E14" s="135" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F14" s="133" t="n">
+      <c r="F14" s="132" t="n">
         <v>3.99</v>
       </c>
-      <c r="G14" s="134">
+      <c r="G14" s="133">
         <f>IF(F14="",0,C14*F14*10)</f>
         <v/>
       </c>
-      <c r="H14" s="135" t="inlineStr">
+      <c r="H14" s="134" t="inlineStr">
         <is>
           <t>53%  [trend penalty: declined &gt;15pp vs 3yr ago]  [through-cycle: 5yr median, latest -152.4% → smoothed 53.3%]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capital Returns</t>
         </is>
       </c>
-      <c r="B15" s="129" t="inlineStr">
+      <c r="B15" s="128" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C15" s="130" t="n">
+      <c r="C15" s="129" t="n">
         <v>0.05</v>
       </c>
-      <c r="D15" s="131" t="inlineStr">
+      <c r="D15" s="130" t="inlineStr">
         <is>
           <t>No capital returns in latest year</t>
         </is>
       </c>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F15" s="133" t="n">
+      <c r="F15" s="132" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="134">
+      <c r="G15" s="133">
         <f>IF(F15="",0,C15*F15*10)</f>
         <v/>
       </c>
-      <c r="H15" s="135" t="inlineStr">
+      <c r="H15" s="134" t="inlineStr">
         <is>
           <t>No capital returns in latest year</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  ROIC</t>
         </is>
       </c>
-      <c r="B16" s="129" t="inlineStr">
+      <c r="B16" s="128" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C16" s="130" t="n">
+      <c r="C16" s="129" t="n">
         <v>0.075</v>
       </c>
-      <c r="D16" s="131" t="inlineStr">
+      <c r="D16" s="130" t="inlineStr">
         <is>
           <t>2.9%  [through-cycle: 5yr median, latest 1.0% → smoothed 2.9%]</t>
         </is>
       </c>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F16" s="133" t="n">
+      <c r="F16" s="132" t="n">
         <v>1.75</v>
       </c>
-      <c r="G16" s="134">
+      <c r="G16" s="133">
         <f>IF(F16="",0,C16*F16*10)</f>
         <v/>
       </c>
-      <c r="H16" s="135" t="inlineStr">
+      <c r="H16" s="134" t="inlineStr">
         <is>
           <t>2.9%  [through-cycle: 5yr median, latest 1.0% → smoothed 2.9%]</t>
         </is>
@@ -10482,113 +10479,113 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Credit Risk  (D / EBITDA)</t>
         </is>
       </c>
-      <c r="B18" s="129" t="inlineStr">
+      <c r="B18" s="128" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C18" s="130" t="n">
+      <c r="C18" s="129" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="131" t="inlineStr">
+      <c r="D18" s="130" t="inlineStr">
         <is>
           <t>12.6x  [through-cycle: 5yr median, latest 19.3x → smoothed 12.6x]</t>
         </is>
       </c>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F18" s="133" t="n">
+      <c r="F18" s="132" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="134">
+      <c r="G18" s="133">
         <f>IF(F18="",0,C18*F18*10)</f>
         <v/>
       </c>
-      <c r="H18" s="135" t="inlineStr">
+      <c r="H18" s="134" t="inlineStr">
         <is>
           <t>12.6x  [through-cycle: 5yr median, latest 19.3x → smoothed 12.6x]</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Interest Cover  (EBIT / Interest)</t>
         </is>
       </c>
-      <c r="B19" s="129" t="inlineStr">
+      <c r="B19" s="128" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C19" s="130" t="n">
+      <c r="C19" s="129" t="n">
         <v>0.075</v>
       </c>
-      <c r="D19" s="131" t="inlineStr">
+      <c r="D19" s="130" t="inlineStr">
         <is>
           <t>2.0x</t>
         </is>
       </c>
-      <c r="E19" s="136" t="inlineStr">
+      <c r="E19" s="135" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
       </c>
-      <c r="F19" s="133" t="n">
+      <c r="F19" s="132" t="n">
         <v>3.04</v>
       </c>
-      <c r="G19" s="134">
+      <c r="G19" s="133">
         <f>IF(F19="",0,C19*F19*10)</f>
         <v/>
       </c>
-      <c r="H19" s="135" t="inlineStr">
+      <c r="H19" s="134" t="inlineStr">
         <is>
           <t>2.0x</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Execution Risk</t>
         </is>
       </c>
-      <c r="B20" s="129" t="inlineStr">
+      <c r="B20" s="128" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C20" s="130" t="n">
+      <c r="C20" s="129" t="n">
         <v>0.05</v>
       </c>
-      <c r="D20" s="131" t="inlineStr">
-        <is>
-          <t>Rev growth σ=5.7%  |  Op margin σ=0.9%  [proxy — lower σ = lower risk = higher score]</t>
-        </is>
-      </c>
-      <c r="E20" s="137" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
-        </is>
-      </c>
-      <c r="F20" s="133" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="G20" s="134">
+      <c r="D20" s="130" t="inlineStr">
+        <is>
+          <t>Rev growth σ=5.7%  |  OM trend -2.3%, σ=0.9%  [quality = direction + stability]</t>
+        </is>
+      </c>
+      <c r="E20" s="135" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="132" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="G20" s="133">
         <f>IF(F20="",0,C20*F20*10)</f>
         <v/>
       </c>
-      <c r="H20" s="135" t="inlineStr">
-        <is>
-          <t>Rev growth σ=5.7%  |  Op margin σ=0.9%  [proxy — lower σ = lower risk = higher score]</t>
+      <c r="H20" s="134" t="inlineStr">
+        <is>
+          <t>Rev growth σ=5.7%  |  OM trend -2.3%, σ=0.9%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10600,76 +10597,76 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="128" t="inlineStr">
+      <c r="A22" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
         </is>
       </c>
-      <c r="B22" s="129" t="inlineStr">
+      <c r="B22" s="128" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C22" s="130" t="n">
+      <c r="C22" s="129" t="n">
         <v>0.1</v>
       </c>
-      <c r="D22" s="131" t="inlineStr">
+      <c r="D22" s="130" t="inlineStr">
         <is>
           <t>Current -6.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
         </is>
       </c>
-      <c r="E22" s="132" t="inlineStr">
+      <c r="E22" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F22" s="133" t="n">
+      <c r="F22" s="132" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="134">
+      <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
         <v/>
       </c>
-      <c r="H22" s="135" t="inlineStr">
+      <c r="H22" s="134" t="inlineStr">
         <is>
           <t>Current -6.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="128" t="inlineStr">
+      <c r="A23" s="127" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
         </is>
       </c>
-      <c r="B23" s="129" t="inlineStr">
+      <c r="B23" s="128" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C23" s="130" t="n">
+      <c r="C23" s="129" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="131" t="inlineStr">
-        <is>
-          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]</t>
-        </is>
-      </c>
-      <c r="E23" s="138" t="inlineStr">
+      <c r="D23" s="130" t="inlineStr">
+        <is>
+          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
+        </is>
+      </c>
+      <c r="E23" s="137" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F23" s="133" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="G23" s="134">
+      <c r="F23" s="132" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
         <v/>
       </c>
-      <c r="H23" s="135" t="inlineStr">
-        <is>
-          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]</t>
+      <c r="H23" s="134" t="inlineStr">
+        <is>
+          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
         </is>
       </c>
     </row>
@@ -10684,42 +10681,42 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="139" t="inlineStr">
+      <c r="A25" s="138" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="140" t="n"/>
-      <c r="C25" s="140" t="n"/>
-      <c r="D25" s="140" t="n"/>
-      <c r="E25" s="140" t="n"/>
-      <c r="F25" s="140" t="n"/>
-      <c r="G25" s="141">
+      <c r="B25" s="139" t="n"/>
+      <c r="C25" s="139" t="n"/>
+      <c r="D25" s="139" t="n"/>
+      <c r="E25" s="139" t="n"/>
+      <c r="F25" s="139" t="n"/>
+      <c r="G25" s="140">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="142" t="inlineStr">
+      <c r="H25" s="141" t="inlineStr">
         <is>
           <t>Floor cap 40.0 applies — see gate warning above.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="143" t="inlineStr">
+      <c r="A26" s="142" t="inlineStr">
         <is>
           <t>FLOOR-ADJUSTED SCORE  (capped at 40.0)</t>
         </is>
       </c>
-      <c r="B26" s="144" t="n"/>
-      <c r="C26" s="144" t="n"/>
-      <c r="D26" s="144" t="n"/>
-      <c r="E26" s="144" t="n"/>
-      <c r="F26" s="144" t="n"/>
-      <c r="G26" s="145">
+      <c r="B26" s="143" t="n"/>
+      <c r="C26" s="143" t="n"/>
+      <c r="D26" s="143" t="n"/>
+      <c r="E26" s="143" t="n"/>
+      <c r="F26" s="143" t="n"/>
+      <c r="G26" s="144">
         <f>MIN(G25,40.0)</f>
         <v/>
       </c>
-      <c r="H26" s="144" t="n"/>
+      <c r="H26" s="143" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="42" t="n"/>
@@ -10732,7 +10729,7 @@
       <c r="H27" s="42" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="146">
+      <c r="A28" s="145">
         <f>IF(G26="","Score incomplete — fill qualitative tiers above",IF(G26&gt;=80,"STRONG BUY",IF(G26&gt;=65,"BUY",IF(G26&gt;=50,"HOLD",IF(G26&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10748,7 +10745,7 @@
       <c r="H29" s="42" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="147" t="inlineStr">
+      <c r="A30" s="146" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>

--- a/static/excel/F_model.xlsx
+++ b/static/excel/F_model.xlsx
@@ -7458,11 +7458,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7672,25 +7672,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0698</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLH0A0HYM2EY — High Yield</t>
         </is>
       </c>
     </row>
@@ -7733,11 +7735,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.08159999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 3.60%</t>
+          <t>Rf 4.56% + spread 3.60%</t>
         </is>
       </c>
     </row>
@@ -7776,11 +7778,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0447</v>
+        <v>0.053</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10097,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — F  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Cyclical</t>
+          <t>JS SCORECARD — F  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Cyclical</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10230,7 @@
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.6% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
@@ -10245,7 +10247,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.5% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
+          <t>GM 12.2% ✗ (&gt;40%)  |  GM trend -3.7% ✗ (&gt;+1pp)  |  ROIC-WACC -2.6% ✗ (&gt;+5pp)  |  Rev consistency σ=5.7% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10612,16 +10614,16 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current -6.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
-        </is>
-      </c>
-      <c r="E22" s="131" t="inlineStr">
-        <is>
-          <t>LOW</t>
+          <t>Fwd P/E 9.1x (scoring basis)  |  5yr avg 7.5x  [+21% vs benchmark]  [trail=3.59 | fwd_pe=9.1x→3.59 | abs=12.0 → blended 40/40/20=5.27]  PEG≈156.48 (trailing_pe=9.1x / rev_cagr=6%, revenue proxy)</t>
+        </is>
+      </c>
+      <c r="E22" s="135" t="inlineStr">
+        <is>
+          <t>MOD-LOW</t>
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10629,7 +10631,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current -6.4x — P/E negative (earnings/FCF below zero, multiple meaningless)</t>
+          <t>Fwd P/E 9.1x (scoring basis)  |  5yr avg 7.5x  [+21% vs benchmark]  [trail=3.59 | fwd_pe=9.1x→3.59 | abs=12.0 → blended 40/40/20=5.27]  PEG≈156.48 (trailing_pe=9.1x / rev_cagr=6%, revenue proxy)</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10651,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
+          <t>Current 4.2x  |  5yr avg 6.0x  [-30% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10666,7 +10668,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 4.2x  |  5yr avg 6.5x  [-35% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
+          <t>Current 4.2x  |  5yr avg 6.0x  [-30% vs benchmark]  [trail=10.00 | fwd_pfcf=4.6x→10.00 | abs=12.0 → blended 40/40/20=10.40]  [fcf_yield=23.8% vs rf=4.6%  spread=+19.2%→modifier=+0.50]</t>
         </is>
       </c>
     </row>
